--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E MULTISEASON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E MULTISEASON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -650,10 +655,15 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -723,10 +733,15 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -796,10 +811,15 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -869,10 +889,15 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -946,10 +971,15 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
@@ -1019,10 +1049,15 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1092,10 +1127,15 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -1165,10 +1205,15 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1238,10 +1283,15 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
@@ -1311,10 +1361,15 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
@@ -1384,10 +1439,15 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -1461,10 +1521,15 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
@@ -1534,10 +1599,15 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1607,10 +1677,15 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -1684,10 +1759,15 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
@@ -1757,10 +1837,15 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1830,10 +1915,15 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1901,8 +1991,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -1970,8 +2069,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>43.7</t>
         </is>
